--- a/artfynd/A 53768-2023 artfynd.xlsx
+++ b/artfynd/A 53768-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53768-2023 artfynd.xlsx
+++ b/artfynd/A 53768-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2195,6 +2195,108 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118094795</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90515</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tvärsförmyran (Tvärsförmyran), Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>570789</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7014580</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
